--- a/assets/constructions/examples/ctd_mie_rou.xlsx
+++ b/assets/constructions/examples/ctd_mie_rou.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,37 +574,57 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EMRT-C20-5R30-110-2T</t>
+          <t>M200D32Z02A32RN12L250</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EMRT</t>
+          <t>M200</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -612,27 +632,27 @@
       <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L2" t="n">
+        <v>39160</v>
+      </c>
       <c r="M2" t="n">
-        <v>0.32</v>
+        <v>1.42</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>RPMT10T3</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,89 +660,99 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DER_RP10T3H</t>
+          <t>WIDIA_RN1204H</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RP10T3_H</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>WID_RN1204_H</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>WID_M200D1_777</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA достижения</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R200-028A32-12M</t>
+          <t>TRS-C25-5R26-200-2T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoroMillⓇ 200 face milling cutter</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>240</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70</v>
+      </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>26300</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>metric RCKT 1204M0</t>
+          <t>RDMT10T3</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -747,32 +777,46 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>COR_RC1204H</t>
+          <t>DER_RD10T3H</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>SAND_RC1204_H</t>
+          <t>RD10T3_H</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>2188.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M170D025Z02A25RD10L180</t>
+          <t>12391013800</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,23 +826,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M170</t>
+          <t>M100</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -807,19 +851,19 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="L4" t="n">
-        <v>12800</v>
+        <v>19000</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
@@ -830,7 +874,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -842,24 +886,24 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HB-32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>WIDIA_RD1003H</t>
+          <t>WIDIA_RD1605H</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>WID_RD1003_H</t>
+          <t>WID_RD1605_H</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>WID_M170D0_643</t>
+          <t>WID_123910_3318</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -867,11 +911,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TRS-C25-5R25-250-2T</t>
+          <t>TRS-C20-5R25-160-2T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -891,13 +941,13 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -908,7 +958,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0.87</v>
+        <v>0.26</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
@@ -943,7 +993,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -964,11 +1014,25 @@
           <t>2019 / DEREK</t>
         </is>
       </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>2014.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMR-C16-4R16-160-2T</t>
+          <t>EMRT-C19-4R20-200-2T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -978,23 +1042,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>EMRT</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -1005,7 +1069,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
@@ -1015,7 +1079,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RPMW0802</t>
+          <t>RPMT08T2</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1040,19 +1104,19 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HA-19</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>DER_RP0802H</t>
+          <t>DER_RP08T2H</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RP0802_H</t>
+          <t>RP08T2_H</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1061,6 +1125,12 @@
           <t>2019 / DEREK</t>
         </is>
       </c>
+      <c r="AD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
